--- a/site/exports/ustc-science-communication.xlsx
+++ b/site/exports/ustc-science-communication.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="18.2" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,66 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>科技传播系</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown；目录、历史角色与开放任期不等于观察日人事确认。；仅必要官网职业摘录与书目；未独立核出版元数据或全文。；法律授位实体未独立核验；学习时间与授位时间分开。；目录原始href、页面文本链接导航和浏览器页面导航分别记载，不互相替代。；3阶段明确获授，授位年保留；具体授位日期unknown。；本人导师unknown；不从合作者或本人招生资格反推。；两书作者列表与个人贡献角色unknown；依据仅限个人页留存书目，不采用未留存的上段说法。；来源另列专业项目：名称：美丽化学；来源角色：创办；来源年份：2014；限制：原文是原创科普项目，不推公司、任职或持续运营状态。；来源：https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm；留存来源自述，不据此新增论文、任职、本人学历或当前状态认证。；来源记载职业信息：职业职称：职称：副教授。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -774,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1992,8 +2046,197 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>化学学士</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>官网明确获得学位，可确认授位及年份；未写学习起止、具体授位日或本人的导师，不补。2002/2005对应清华化学学士/硕士。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科；来源date_as_source：2002</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>化学硕士</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>官网明确获得学位，可确认授位及年份；未写学习起止、具体授位日或本人的导师，不补。2002/2005对应清华化学学士/硕士。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士；来源date_as_source：2005</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>材料科学博士</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>美国明尼苏达大学</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>材料科学</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>官网明确获得学位，可确认授位及年份；未写学习起止、具体授位日或本人的导师，不补。2002/2005对应清华化学学士/硕士。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士；来源date_as_source：2011</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S20"/>
+  <autoFilter ref="A1:S23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -2014,6 +2257,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2373,18 +2619,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="36.4" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -2716,8 +2962,112 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>美丽的化学反应</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>book_as_official_list</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；year：2015；year_as_source：2 015；官网书目记录，外部出版元数据未核，全文未读；无来源角色不补。；来源书目信息（author_list_status）：not_explicitly_listed</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>美丽的化学结构</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>book_as_official_list</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；year：2015；year_as_source：2 015；官网书目记录，外部出版元数据未核，全文未读；无来源角色不补。；来源书目信息（author_list_status）：not_explicitly_listed</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -2725,6 +3075,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2736,14 +3090,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46.2" customWidth="1" min="2" max="2"/>
+    <col width="61.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3008,8 +3362,82 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ustc-liangyan-s001-3fa4a618f046</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/2021/0601/c4503a511043/page.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:10:46.204Z</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>梁琰</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ustc-liangyan-s002-2c63bf2a28b8</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://stc.ustc.edu.cn/4500/list.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:10:42.723Z</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ustc</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3018,6 +3446,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/ustc-science-communication.xlsx
+++ b/site/exports/ustc-science-communication.xlsx
@@ -2079,7 +2079,7 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L21" s="2" t="b">
@@ -2142,7 +2142,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L22" s="2" t="b">
